--- a/Asian Paints.xlsx
+++ b/Asian Paints.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bf63bd8a528ee9/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Files\Three_Statement_Model_Asian_Paints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{8030C4EF-1A0B-4C49-B150-4A1B58CC14AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6A923A-B3B9-449F-BBB4-8E25C3258306}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC7ABF9-231D-4767-8FCD-5B0C25B0C134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profit &amp; Loss" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="Customization" sheetId="5" r:id="rId5"/>
     <sheet name="Data Sheet" sheetId="6" r:id="rId6"/>
     <sheet name="Assumption_A.p." sheetId="7" r:id="rId7"/>
-    <sheet name="Three_ Statement_Models" sheetId="8" r:id="rId8"/>
+    <sheet name="Three_ Statement_Models (2)" sheetId="9" r:id="rId8"/>
+    <sheet name="Three_ Statement_Models" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="UPDATE">'Data Sheet'!$E$1</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="123">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -1551,10 +1552,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Annual" displayName="Annual" ref="A3:N19" headerRowCount="0" totalsRowShown="0" headerRowDxfId="30">
   <tableColumns count="14">
@@ -7491,6 +7488,1275 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B06D82-F71D-4EDA-9467-E934D57BBB4B}">
+  <dimension ref="B3:R62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C3" s="29">
+        <v>45747</v>
+      </c>
+      <c r="D3" s="29">
+        <v>46112</v>
+      </c>
+      <c r="E3" s="29">
+        <v>46477</v>
+      </c>
+      <c r="F3" s="29">
+        <v>46843</v>
+      </c>
+      <c r="G3" s="29">
+        <v>47208</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="28">
+        <v>33905.620000000003</v>
+      </c>
+      <c r="D5" s="28">
+        <f>C5*1.06</f>
+        <v>35939.957200000004</v>
+      </c>
+      <c r="E5" s="28">
+        <f t="shared" ref="E5:G5" si="0">D5*1.06</f>
+        <v>38096.35463200001</v>
+      </c>
+      <c r="F5" s="28">
+        <f t="shared" si="0"/>
+        <v>40382.135909920013</v>
+      </c>
+      <c r="G5" s="28">
+        <f t="shared" si="0"/>
+        <v>42805.064064515216</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="28">
+        <v>27899.41</v>
+      </c>
+      <c r="D6" s="28">
+        <f>-D5*0.82</f>
+        <v>-29470.764904000003</v>
+      </c>
+      <c r="E6" s="28">
+        <f t="shared" ref="E6:G6" si="1">-E5*0.82</f>
+        <v>-31239.010798240008</v>
+      </c>
+      <c r="F6" s="28">
+        <f t="shared" si="1"/>
+        <v>-33113.351446134409</v>
+      </c>
+      <c r="G6" s="28">
+        <f t="shared" si="1"/>
+        <v>-35100.152532902473</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="28">
+        <v>6006.2100000000028</v>
+      </c>
+      <c r="D7" s="28">
+        <f>SUM(D5:D6)</f>
+        <v>6469.1922960000011</v>
+      </c>
+      <c r="E7" s="28">
+        <f t="shared" ref="E7:G7" si="2">SUM(E5:E6)</f>
+        <v>6857.3438337600019</v>
+      </c>
+      <c r="F7" s="28">
+        <f t="shared" si="2"/>
+        <v>7268.7844637856033</v>
+      </c>
+      <c r="G7" s="28">
+        <f t="shared" si="2"/>
+        <v>7704.9115316127427</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="28">
+        <v>350.22</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="M8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="28">
+        <v>1026.3399999999999</v>
+      </c>
+      <c r="D9" s="28">
+        <f>-D5*0.03</f>
+        <v>-1078.1987160000001</v>
+      </c>
+      <c r="E9" s="28">
+        <f t="shared" ref="E9:G9" si="3">-E5*0.03</f>
+        <v>-1142.8906389600002</v>
+      </c>
+      <c r="F9" s="28">
+        <f t="shared" si="3"/>
+        <v>-1211.4640772976004</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" si="3"/>
+        <v>-1284.1519219354564</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="28">
+        <v>227.02</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="M10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="28">
+        <v>5103.07</v>
+      </c>
+      <c r="D11" s="28">
+        <f>SUM(D7:D10)</f>
+        <v>5390.9935800000012</v>
+      </c>
+      <c r="E11" s="28">
+        <f t="shared" ref="E11:G11" si="4">SUM(E7:E10)</f>
+        <v>5714.4531948000022</v>
+      </c>
+      <c r="F11" s="28">
+        <f t="shared" si="4"/>
+        <v>6057.3203864880034</v>
+      </c>
+      <c r="G11" s="28">
+        <f t="shared" si="4"/>
+        <v>6420.7596096772868</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="28">
+        <v>1393.36</v>
+      </c>
+      <c r="D12" s="28">
+        <f>-D11*0.26</f>
+        <v>-1401.6583308000004</v>
+      </c>
+      <c r="E12" s="28">
+        <f>-E11*0.26</f>
+        <v>-1485.7578306480007</v>
+      </c>
+      <c r="F12" s="28">
+        <f>-F11*0.26</f>
+        <v>-1574.9033004868809</v>
+      </c>
+      <c r="G12" s="28">
+        <f>-G11*0.26</f>
+        <v>-1669.3974985160946</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="28">
+        <v>3667.23</v>
+      </c>
+      <c r="D13" s="28">
+        <f>SUM(D11:D12)</f>
+        <v>3989.3352492000008</v>
+      </c>
+      <c r="E13" s="28">
+        <f>SUM(E11:E12)</f>
+        <v>4228.6953641520013</v>
+      </c>
+      <c r="F13" s="28">
+        <f>SUM(F11:F12)</f>
+        <v>4482.4170860011227</v>
+      </c>
+      <c r="G13" s="28">
+        <f>SUM(G11:G12)</f>
+        <v>4751.3621111611919</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N18" s="29">
+        <v>45747</v>
+      </c>
+      <c r="O18" s="29">
+        <v>46112</v>
+      </c>
+      <c r="P18" s="29">
+        <v>46477</v>
+      </c>
+      <c r="Q18" s="29">
+        <v>46843</v>
+      </c>
+      <c r="R18" s="29">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28">
+        <f>N22</f>
+        <v>19304</v>
+      </c>
+      <c r="P19" s="28">
+        <f t="shared" ref="P19:R19" si="5">O22</f>
+        <v>21298.667624600002</v>
+      </c>
+      <c r="Q19" s="28">
+        <f t="shared" si="5"/>
+        <v>23413.015306676003</v>
+      </c>
+      <c r="R19" s="28">
+        <f t="shared" si="5"/>
+        <v>25654.223849676564</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C20" s="29">
+        <v>45747</v>
+      </c>
+      <c r="D20" s="29">
+        <v>46112</v>
+      </c>
+      <c r="E20" s="29">
+        <v>46477</v>
+      </c>
+      <c r="F20" s="29">
+        <v>46843</v>
+      </c>
+      <c r="G20" s="29">
+        <v>47208</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28">
+        <f>D13</f>
+        <v>3989.3352492000008</v>
+      </c>
+      <c r="P20" s="28">
+        <f t="shared" ref="P20:R20" si="6">E13</f>
+        <v>4228.6953641520013</v>
+      </c>
+      <c r="Q20" s="28">
+        <f t="shared" si="6"/>
+        <v>4482.4170860011227</v>
+      </c>
+      <c r="R20" s="28">
+        <f t="shared" si="6"/>
+        <v>4751.3621111611919</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28">
+        <f>-O20*0.5</f>
+        <v>-1994.6676246000004</v>
+      </c>
+      <c r="P21" s="28">
+        <f t="shared" ref="P21:R21" si="7">-P20*0.5</f>
+        <v>-2114.3476820760006</v>
+      </c>
+      <c r="Q21" s="28">
+        <f t="shared" si="7"/>
+        <v>-2241.2085430005613</v>
+      </c>
+      <c r="R21" s="28">
+        <f t="shared" si="7"/>
+        <v>-2375.681055580596</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="28">
+        <v>95.92</v>
+      </c>
+      <c r="D22" s="28">
+        <f>C22</f>
+        <v>95.92</v>
+      </c>
+      <c r="E22" s="28">
+        <f t="shared" ref="E22:G22" si="8">D22</f>
+        <v>95.92</v>
+      </c>
+      <c r="F22" s="28">
+        <f t="shared" si="8"/>
+        <v>95.92</v>
+      </c>
+      <c r="G22" s="28">
+        <f t="shared" si="8"/>
+        <v>95.92</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N22" s="28">
+        <v>19304</v>
+      </c>
+      <c r="O22" s="28">
+        <f>SUM(O19:O21)</f>
+        <v>21298.667624600002</v>
+      </c>
+      <c r="P22" s="28">
+        <f t="shared" ref="P22:R22" si="9">SUM(P19:P21)</f>
+        <v>23413.015306676003</v>
+      </c>
+      <c r="Q22" s="28">
+        <f t="shared" si="9"/>
+        <v>25654.223849676564</v>
+      </c>
+      <c r="R22" s="28">
+        <f t="shared" si="9"/>
+        <v>28029.904905257161</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="28">
+        <v>19303.89</v>
+      </c>
+      <c r="D24" s="28">
+        <f>O22</f>
+        <v>21298.667624600002</v>
+      </c>
+      <c r="E24" s="28">
+        <f t="shared" ref="E24:G24" si="10">P22</f>
+        <v>23413.015306676003</v>
+      </c>
+      <c r="F24" s="28">
+        <f t="shared" si="10"/>
+        <v>25654.223849676564</v>
+      </c>
+      <c r="G24" s="28">
+        <f t="shared" si="10"/>
+        <v>28029.904905257161</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="28">
+        <v>2290.29</v>
+      </c>
+      <c r="D25" s="28">
+        <f>C25*1.14</f>
+        <v>2610.9305999999997</v>
+      </c>
+      <c r="E25" s="28">
+        <f t="shared" ref="E25:G25" si="11">D25*1.14</f>
+        <v>2976.4608839999992</v>
+      </c>
+      <c r="F25" s="28">
+        <f t="shared" si="11"/>
+        <v>3393.1654077599987</v>
+      </c>
+      <c r="G25" s="28">
+        <f t="shared" si="11"/>
+        <v>3868.2085648463981</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="28">
+        <v>8665.15</v>
+      </c>
+      <c r="D26" s="28">
+        <f>D5*0.25</f>
+        <v>8984.9893000000011</v>
+      </c>
+      <c r="E26" s="28">
+        <f t="shared" ref="E26:G26" si="12">E5*0.25</f>
+        <v>9524.0886580000024</v>
+      </c>
+      <c r="F26" s="28">
+        <f t="shared" si="12"/>
+        <v>10095.533977480003</v>
+      </c>
+      <c r="G26" s="28">
+        <f t="shared" si="12"/>
+        <v>10701.266016128804</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="29">
+        <v>45747</v>
+      </c>
+      <c r="O26" s="29">
+        <v>46112</v>
+      </c>
+      <c r="P26" s="29">
+        <v>46477</v>
+      </c>
+      <c r="Q26" s="29">
+        <v>46843</v>
+      </c>
+      <c r="R26" s="29">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="28">
+        <f>SUM(C22:C26)</f>
+        <v>30355.25</v>
+      </c>
+      <c r="D27" s="28">
+        <f>SUM(D22:D26)</f>
+        <v>32990.507524600005</v>
+      </c>
+      <c r="E27" s="28">
+        <f t="shared" ref="E27:G27" si="13">SUM(E22:E26)</f>
+        <v>36009.484848676002</v>
+      </c>
+      <c r="F27" s="28">
+        <f t="shared" si="13"/>
+        <v>39238.843234916567</v>
+      </c>
+      <c r="G27" s="28">
+        <f t="shared" si="13"/>
+        <v>42695.299486232361</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31">
+        <f>N30</f>
+        <v>9220</v>
+      </c>
+      <c r="P27" s="31">
+        <f t="shared" ref="P27:R27" si="14">O30</f>
+        <v>10298.198715999999</v>
+      </c>
+      <c r="Q27" s="31">
+        <f t="shared" si="14"/>
+        <v>11441.089354959999</v>
+      </c>
+      <c r="R27" s="31">
+        <f t="shared" si="14"/>
+        <v>12652.5534322576</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B28" s="2"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="M28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31">
+        <f>D5*0.06</f>
+        <v>2156.3974320000002</v>
+      </c>
+      <c r="P28" s="31">
+        <f t="shared" ref="P28:R28" si="15">E5*0.06</f>
+        <v>2285.7812779200003</v>
+      </c>
+      <c r="Q28" s="31">
+        <f t="shared" si="15"/>
+        <v>2422.9281545952008</v>
+      </c>
+      <c r="R28" s="31">
+        <f t="shared" si="15"/>
+        <v>2568.3038438709127</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B29" s="2"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="M29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31">
+        <f>D9</f>
+        <v>-1078.1987160000001</v>
+      </c>
+      <c r="P29" s="31">
+        <f>E9</f>
+        <v>-1142.8906389600002</v>
+      </c>
+      <c r="Q29" s="31">
+        <f>F9</f>
+        <v>-1211.4640772976004</v>
+      </c>
+      <c r="R29" s="31">
+        <f>G9</f>
+        <v>-1284.1519219354564</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="28">
+        <v>781.98</v>
+      </c>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="M30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N30" s="31">
+        <v>9220</v>
+      </c>
+      <c r="O30" s="31">
+        <f>SUM(O27:O29)</f>
+        <v>10298.198715999999</v>
+      </c>
+      <c r="P30" s="31">
+        <f>SUM(P27:P29)</f>
+        <v>11441.089354959999</v>
+      </c>
+      <c r="Q30" s="31">
+        <f>SUM(Q27:Q29)</f>
+        <v>12652.5534322576</v>
+      </c>
+      <c r="R30" s="31">
+        <f>SUM(R27:R29)</f>
+        <v>13936.705354193058</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="28">
+        <v>9220.1</v>
+      </c>
+      <c r="D31" s="28">
+        <f>O30</f>
+        <v>10298.198715999999</v>
+      </c>
+      <c r="E31" s="28">
+        <f t="shared" ref="E31:G31" si="16">P30</f>
+        <v>11441.089354959999</v>
+      </c>
+      <c r="F31" s="28">
+        <f t="shared" si="16"/>
+        <v>12652.5534322576</v>
+      </c>
+      <c r="G31" s="28">
+        <f t="shared" si="16"/>
+        <v>13936.705354193058</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="28">
+        <v>1254.49</v>
+      </c>
+      <c r="D32" s="28">
+        <f>C32*1.83</f>
+        <v>2295.7166999999999</v>
+      </c>
+      <c r="E32" s="28">
+        <f t="shared" ref="E32:G32" si="17">D32*1.83</f>
+        <v>4201.1615609999999</v>
+      </c>
+      <c r="F32" s="28">
+        <f t="shared" si="17"/>
+        <v>7688.1256566299999</v>
+      </c>
+      <c r="G32" s="28">
+        <f t="shared" si="17"/>
+        <v>14069.269951632901</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="28">
+        <v>4724.75</v>
+      </c>
+      <c r="D33" s="28">
+        <f>C33*2.14</f>
+        <v>10110.965</v>
+      </c>
+      <c r="E33" s="28">
+        <f t="shared" ref="E33:G33" si="18">D33*2.14</f>
+        <v>21637.465100000001</v>
+      </c>
+      <c r="F33" s="28">
+        <f t="shared" si="18"/>
+        <v>46304.175314000007</v>
+      </c>
+      <c r="G33" s="28">
+        <f t="shared" si="18"/>
+        <v>99090.935171960024</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="28">
+        <v>14373.93</v>
+      </c>
+      <c r="D34" s="28">
+        <f>D5*0.42</f>
+        <v>15094.782024000002</v>
+      </c>
+      <c r="E34" s="28">
+        <f t="shared" ref="E34:G34" si="19">E5*0.42</f>
+        <v>16000.468945440003</v>
+      </c>
+      <c r="F34" s="28">
+        <f t="shared" si="19"/>
+        <v>16960.497082166406</v>
+      </c>
+      <c r="G34" s="28">
+        <f t="shared" si="19"/>
+        <v>17978.12690709639</v>
+      </c>
+      <c r="O34" s="26">
+        <f>SUM(O28:O29)</f>
+        <v>1078.1987160000001</v>
+      </c>
+      <c r="P34" s="26">
+        <f t="shared" ref="P34:R34" si="20">SUM(P28:P29)</f>
+        <v>1142.8906389600002</v>
+      </c>
+      <c r="Q34" s="26">
+        <f t="shared" si="20"/>
+        <v>1211.4640772976004</v>
+      </c>
+      <c r="R34" s="26">
+        <f t="shared" si="20"/>
+        <v>1284.1519219354564</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="28">
+        <f>SUM(C30:C34)</f>
+        <v>30355.25</v>
+      </c>
+      <c r="D35" s="28">
+        <f>SUM(D30:D34)</f>
+        <v>37799.66244</v>
+      </c>
+      <c r="E35" s="28">
+        <f t="shared" ref="E35:G35" si="21">SUM(E30:E34)</f>
+        <v>53280.184961400009</v>
+      </c>
+      <c r="F35" s="28">
+        <f t="shared" si="21"/>
+        <v>83605.351485054009</v>
+      </c>
+      <c r="G35" s="28">
+        <f t="shared" si="21"/>
+        <v>145075.03738488237</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="2"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="2"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="28">
+        <f>C27-C35</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="28">
+        <f t="shared" ref="D38:G38" si="22">D27-D35</f>
+        <v>-4809.1549153999949</v>
+      </c>
+      <c r="E38" s="28">
+        <f t="shared" si="22"/>
+        <v>-17270.700112724007</v>
+      </c>
+      <c r="F38" s="28">
+        <f t="shared" si="22"/>
+        <v>-44366.508250137442</v>
+      </c>
+      <c r="G38" s="28">
+        <f t="shared" si="22"/>
+        <v>-102379.73789865</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C42" s="29">
+        <v>45747</v>
+      </c>
+      <c r="D42" s="29">
+        <v>46112</v>
+      </c>
+      <c r="E42" s="29">
+        <v>46477</v>
+      </c>
+      <c r="F42" s="29">
+        <v>46843</v>
+      </c>
+      <c r="G42" s="29">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28">
+        <f>D13</f>
+        <v>3989.3352492000008</v>
+      </c>
+      <c r="E45" s="28">
+        <f t="shared" ref="E45:G45" si="23">E13</f>
+        <v>4228.6953641520013</v>
+      </c>
+      <c r="F45" s="28">
+        <f t="shared" si="23"/>
+        <v>4482.4170860011227</v>
+      </c>
+      <c r="G45" s="28">
+        <f t="shared" si="23"/>
+        <v>4751.3621111611919</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="28"/>
+      <c r="J46" s="28">
+        <f>-D9</f>
+        <v>1078.1987160000001</v>
+      </c>
+      <c r="K46" s="28">
+        <f>-E9</f>
+        <v>1142.8906389600002</v>
+      </c>
+      <c r="L46" s="28">
+        <f>-F9</f>
+        <v>1211.4640772976004</v>
+      </c>
+      <c r="M46" s="28">
+        <f>-G9</f>
+        <v>1284.1519219354564</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B47" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28">
+        <f>C34-D34</f>
+        <v>-720.85202400000162</v>
+      </c>
+      <c r="E47" s="28">
+        <f t="shared" ref="E47:G47" si="24">D34-E34</f>
+        <v>-905.68692144000124</v>
+      </c>
+      <c r="F47" s="28">
+        <f t="shared" si="24"/>
+        <v>-960.02813672640332</v>
+      </c>
+      <c r="G47" s="28">
+        <f t="shared" si="24"/>
+        <v>-1017.6298249299834</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28">
+        <f>D26-C26</f>
+        <v>319.83930000000146</v>
+      </c>
+      <c r="E48" s="28">
+        <f t="shared" ref="E48:G48" si="25">E26-D26</f>
+        <v>539.0993580000013</v>
+      </c>
+      <c r="F48" s="28">
+        <f t="shared" si="25"/>
+        <v>571.44531948000076</v>
+      </c>
+      <c r="G48" s="28">
+        <f t="shared" si="25"/>
+        <v>605.73203864880088</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28">
+        <f>SUM(D45:D48)</f>
+        <v>3588.3225252000007</v>
+      </c>
+      <c r="E49" s="28">
+        <f t="shared" ref="E49:G49" si="26">SUM(E45:E48)</f>
+        <v>3862.1078007120013</v>
+      </c>
+      <c r="F49" s="28">
+        <f t="shared" si="26"/>
+        <v>4093.8342687547201</v>
+      </c>
+      <c r="G49" s="28">
+        <f t="shared" si="26"/>
+        <v>4339.4643248800094</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" s="2"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="28"/>
+      <c r="D51" s="32">
+        <f>O29</f>
+        <v>-1078.1987160000001</v>
+      </c>
+      <c r="E51" s="32">
+        <f t="shared" ref="E51:G51" si="27">P29</f>
+        <v>-1142.8906389600002</v>
+      </c>
+      <c r="F51" s="32">
+        <f t="shared" si="27"/>
+        <v>-1211.4640772976004</v>
+      </c>
+      <c r="G51" s="32">
+        <f t="shared" si="27"/>
+        <v>-1284.1519219354564</v>
+      </c>
+      <c r="I51" s="28">
+        <f>-O28</f>
+        <v>-2156.3974320000002</v>
+      </c>
+      <c r="J51" s="28">
+        <f>-P28</f>
+        <v>-2285.7812779200003</v>
+      </c>
+      <c r="K51" s="28">
+        <f>-Q28</f>
+        <v>-2422.9281545952008</v>
+      </c>
+      <c r="L51" s="28">
+        <f>-R28</f>
+        <v>-2568.3038438709127</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28">
+        <f>C33-D33</f>
+        <v>-5386.2150000000001</v>
+      </c>
+      <c r="E52" s="28">
+        <f t="shared" ref="E52:G52" si="28">D33-E33</f>
+        <v>-11526.500100000001</v>
+      </c>
+      <c r="F52" s="28">
+        <f t="shared" si="28"/>
+        <v>-24666.710214000006</v>
+      </c>
+      <c r="G52" s="28">
+        <f t="shared" si="28"/>
+        <v>-52786.759857960016</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28">
+        <f>C32-D32</f>
+        <v>-1041.2266999999999</v>
+      </c>
+      <c r="E53" s="28">
+        <f t="shared" ref="E53:G53" si="29">D32-E32</f>
+        <v>-1905.4448609999999</v>
+      </c>
+      <c r="F53" s="28">
+        <f t="shared" si="29"/>
+        <v>-3486.96409563</v>
+      </c>
+      <c r="G53" s="28">
+        <f t="shared" si="29"/>
+        <v>-6381.1442950029013</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28">
+        <f>SUM(D51:D53)</f>
+        <v>-7505.6404160000002</v>
+      </c>
+      <c r="E54" s="28">
+        <f t="shared" ref="E54:G54" si="30">SUM(E51:E53)</f>
+        <v>-14574.835599960001</v>
+      </c>
+      <c r="F54" s="28">
+        <f t="shared" si="30"/>
+        <v>-29365.138386927607</v>
+      </c>
+      <c r="G54" s="28">
+        <f t="shared" si="30"/>
+        <v>-60452.056074898377</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B55" s="2"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28">
+        <f>D25-C25</f>
+        <v>320.64059999999972</v>
+      </c>
+      <c r="E56" s="28">
+        <f t="shared" ref="E56:G56" si="31">E25-D25</f>
+        <v>365.53028399999948</v>
+      </c>
+      <c r="F56" s="28">
+        <f t="shared" si="31"/>
+        <v>416.70452375999957</v>
+      </c>
+      <c r="G56" s="28">
+        <f t="shared" si="31"/>
+        <v>475.04315708639933</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B57" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28">
+        <f>O21</f>
+        <v>-1994.6676246000004</v>
+      </c>
+      <c r="E57" s="28">
+        <f t="shared" ref="E57:G57" si="32">P21</f>
+        <v>-2114.3476820760006</v>
+      </c>
+      <c r="F57" s="28">
+        <f t="shared" si="32"/>
+        <v>-2241.2085430005613</v>
+      </c>
+      <c r="G57" s="28">
+        <f t="shared" si="32"/>
+        <v>-2375.681055580596</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28">
+        <f>SUM(D56:D57)</f>
+        <v>-1674.0270246000007</v>
+      </c>
+      <c r="E58" s="28">
+        <f t="shared" ref="E58:G58" si="33">SUM(E56:E57)</f>
+        <v>-1748.8173980760012</v>
+      </c>
+      <c r="F58" s="28">
+        <f t="shared" si="33"/>
+        <v>-1824.5040192405618</v>
+      </c>
+      <c r="G58" s="28">
+        <f t="shared" si="33"/>
+        <v>-1900.6378984941966</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B59" s="2"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28">
+        <f>SUM(D49,D54,D58)</f>
+        <v>-5591.3449154</v>
+      </c>
+      <c r="E60" s="28">
+        <f t="shared" ref="E60:G60" si="34">SUM(E49,E54,E58)</f>
+        <v>-12461.545197324001</v>
+      </c>
+      <c r="F60" s="28">
+        <f t="shared" si="34"/>
+        <v>-27095.808137413449</v>
+      </c>
+      <c r="G60" s="28">
+        <f t="shared" si="34"/>
+        <v>-58013.22964851257</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28">
+        <f>C62</f>
+        <v>782</v>
+      </c>
+      <c r="E61" s="28">
+        <f t="shared" ref="E61:G61" si="35">D62</f>
+        <v>-4809.3449154</v>
+      </c>
+      <c r="F61" s="28">
+        <f t="shared" si="35"/>
+        <v>-17270.890112724002</v>
+      </c>
+      <c r="G61" s="28">
+        <f t="shared" si="35"/>
+        <v>-44366.698250137451</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B62" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="2">
+        <v>782</v>
+      </c>
+      <c r="D62" s="32">
+        <f>SUM(D60:D61)</f>
+        <v>-4809.3449154</v>
+      </c>
+      <c r="E62" s="32">
+        <f t="shared" ref="E62:G62" si="36">SUM(E60:E61)</f>
+        <v>-17270.890112724002</v>
+      </c>
+      <c r="F62" s="32">
+        <f t="shared" si="36"/>
+        <v>-44366.698250137451</v>
+      </c>
+      <c r="G62" s="32">
+        <f t="shared" si="36"/>
+        <v>-102379.92789865003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F6514-8A1A-453D-A007-A0EDF5E41B78}">
   <dimension ref="B3:R62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
